--- a/Guide/物料清单-电子.xlsx
+++ b/Guide/物料清单-电子.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ROS2轮足\Aidlux\Rhino-Pi-X1-ROS2HomeRobots\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2366414-9CAB-4D99-9E30-4A0E7402AD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B9A1378-D6AA-4AF5-922F-69C4FCEC58BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,11 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
-  <si>
-    <t>电机部分</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="48">
   <si>
     <t>商品名称</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -55,14 +51,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>达妙DM-02开发板(STM32H723)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>电子部分的清单</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>犀牛派X1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -72,6 +60,174 @@
   </si>
   <si>
     <t>达妙DM-H6215</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>线缆</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XT30 2+2 10cm连接线</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XT30 公转母10cm连接线</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://e.tb.cn/h.RjT2kASAGH76AEk?tk=2eSJgcMU2Am</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XT30 公转公20cm连接线</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://e.tb.cn/h.RjTeSO6zBMt2cCn?tk=717rgcM6pw5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://e.tb.cn/h.R9kllLwFKdFckqE?tk=ltyjgcMiNeD CZ028</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GH1.25-2P 双头同向连接线</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GH1.25-2P 双头反向连接线</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://e.tb.cn/h.R9kpRRDtlBeZRJu?tk=Z7cCgcMPwCE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>USB转Type-C 0.15m数据线</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://e.tb.cn/h.RQ3BR1Sea3ICNS0?tk=siflgcMpBYr</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC5525弯头转XT30 0.25m公头数据线</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://e.tb.cn/h.RjTprohOPqD21Px?tk=ybzggcMHRWN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>商品链接</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>USB3.0拓展坞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://e.tb.cn/h.RjTtcGkJ4LBtpIL?tk=NvTigcMExtQ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>电机</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://e.tb.cn/h.RjTvLsRJvvWV5K0?tk=T0ZtgcMxsrI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>7寸IPS-HDMI触摸显示器</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">https://e.tb.cn/h.R9P5ClybYj900QC?tk=TTfVgco2fdN </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥比中光AstraPro深度相机</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://e.tb.cn/h.Rj6YN9uOyQtTkNR?tk=raTfgcoWWLT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>乐动LD-06激光雷达</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://e.tb.cn/h.R8mYZBMvyD9IlTS?tk=BgUYgcoVh4M</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HDMI 上弯头4mm 0.5m数据线</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://e.tb.cn/h.R9PjPXLabjV7MsR?tk=s0DOgcoUdiA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>USB转Type-C 0.25m弯头数据线</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://e.tb.cn/h.Rj663mq5BvGzA7M?tk=0F3kgco8zyW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CP2102 TTL模块</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://e.tb.cn/h.Rj6PCqmeg3VsXt5?tk=mfMkgcomlPG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>USB 10052音箱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://e.tb.cn/h.Rj6mjqfMyyArA9B?tk=Ezlhgconkh4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>达妙DM-MC02开发板(STM32H723)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://e.tb.cn/h.RQeCFhEXogUV3RT?tk=PiO8gcopaTp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DJI Matrice 4D 电池</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://e.tb.cn/h.Rj6Jqoaeakz4go8?tk=dnf4gcoIIWM</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoboMaster 电池架</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://e.tb.cn/h.RQV1TtnHIyDQaoA?tk=TppwgcoGlvn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>上电缓启动模块</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://e.tb.cn/h.Rj6FbfnDzR5oCwH?tk=1SqOgcovrQk</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>电子部分的物料清单</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -79,7 +235,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,15 +268,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="20"/>
-      <color theme="1"/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="等线"/>
-      <family val="3"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="等线"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -132,8 +296,13 @@
         <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -193,14 +362,53 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -208,51 +416,65 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="2" builtinId="8"/>
+    <cellStyle name="适中" xfId="3" builtinId="28"/>
     <cellStyle name="输出" xfId="1" builtinId="21"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -531,42 +753,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
+    <row r="1" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
     </row>
     <row r="3" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
@@ -585,109 +807,523 @@
       <c r="N3" s="2"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="4" t="s">
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="3">
+        <v>4</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="4">
         <v>2</v>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="12"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="4">
+        <v>1</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="4">
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
+      <c r="F17" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="16"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="6">
-        <v>1</v>
-      </c>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="7">
+        <v>1</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="7">
+        <v>1</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="11"/>
+      <c r="H19" s="12"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="7">
+        <v>1</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="11"/>
+      <c r="H20" s="12"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="7">
+        <v>1</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" s="11"/>
+      <c r="H21" s="12"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="7">
+        <v>1</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22" s="11"/>
+      <c r="H22" s="12"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="7">
+        <v>1</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23" s="11"/>
+      <c r="H23" s="12"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="7">
+        <v>1</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="11"/>
+      <c r="H24" s="12"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="7">
+        <v>1</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" s="11"/>
+      <c r="H25" s="12"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="7">
+        <v>1</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G26" s="11"/>
+      <c r="H26" s="12"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="7">
+        <v>1</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="7">
+        <v>1</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="7">
+        <v>1</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="7">
+        <v>1</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="7">
+        <v>1</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="8">
+        <v>1</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="8">
+        <v>1</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="8">
+        <v>1</v>
+      </c>
+      <c r="F37" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="54">
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="A4:H4"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A1:N2"/>
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="A22:D22"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="F18" r:id="rId1" xr:uid="{CCBB1510-1C4B-4B1B-A8B5-ED574B99683D}"/>
+    <hyperlink ref="F19" r:id="rId2" xr:uid="{3526AE6D-92D9-42DC-8E3B-F0C42B55046C}"/>
+    <hyperlink ref="F17" r:id="rId3" xr:uid="{E9F95FCE-E568-449C-AF55-0B72EC062299}"/>
+    <hyperlink ref="F20" r:id="rId4" xr:uid="{85B72A6A-6AC3-4FFA-9CE4-54AC07D3652C}"/>
+    <hyperlink ref="F21" r:id="rId5" xr:uid="{1ED0AE90-D37F-40F9-92DC-F839E5FEC021}"/>
+    <hyperlink ref="F22" r:id="rId6" xr:uid="{99517504-834F-4257-BD87-A0C6B1DBCAC9}"/>
+    <hyperlink ref="F23" r:id="rId7" xr:uid="{B8787208-8C49-4DCA-B99B-8A7AB0B8D10F}"/>
+    <hyperlink ref="F24" r:id="rId8" xr:uid="{9A93364C-C398-4CC9-AAEE-8EB47C03211D}"/>
+    <hyperlink ref="F6" r:id="rId9" xr:uid="{B581DDEA-A28C-429C-AE63-AB5F101957B3}"/>
+    <hyperlink ref="F29" r:id="rId10" xr:uid="{5F7BD5F1-7719-40A6-8B55-E69EC212DB4D}"/>
+    <hyperlink ref="F30" r:id="rId11" xr:uid="{576F3BEC-FF12-4AA9-9031-F76B55B8F80D}"/>
+    <hyperlink ref="F31" r:id="rId12" xr:uid="{CCF5AE6B-4227-4BCE-8EA1-79EC71E6CF62}"/>
+    <hyperlink ref="F25" r:id="rId13" xr:uid="{90A6DF79-F2F8-4DDA-A653-CA8427D1A7D6}"/>
+    <hyperlink ref="F26" r:id="rId14" xr:uid="{2DF3F7DF-356A-4EFB-84CC-E7A50F559ADC}"/>
+    <hyperlink ref="F32" r:id="rId15" xr:uid="{86F5B3FD-4A45-4F41-B150-5A03DEC61FE5}"/>
+    <hyperlink ref="F33" r:id="rId16" xr:uid="{1C3FBAEC-BDB9-4E29-9100-84B48AC92355}"/>
+    <hyperlink ref="F12" r:id="rId17" xr:uid="{15C31FD3-3DC5-408E-B506-02A21CE4F05F}"/>
+    <hyperlink ref="F35" r:id="rId18" xr:uid="{236DFBCA-5CC2-4A93-AC0E-542DC61E585C}"/>
+    <hyperlink ref="F36" r:id="rId19" xr:uid="{DFBF7CF1-0F4A-4D95-A536-C0E5DB74F63A}"/>
+    <hyperlink ref="F37" r:id="rId20" xr:uid="{EE5DFC67-BFA1-4E48-8D01-27336F06798A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId21"/>
 </worksheet>
 </file>